--- a/operation_logs.xlsx
+++ b/operation_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +453,303 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L202602210000537663</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-02-21 00:00:53</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:22</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L202602210002006269</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-02-21 00:02:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:11007</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>L202602210002163137</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-02-21 00:02:16</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:11007</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L202602210003001118</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-02-21 00:03:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L202602210004592866</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-02-21 00:04:59</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:1100</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>L202602210006508651</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-02-21 00:06:50</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:11007</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>L202602210007157100</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-02-21 00:07:15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L202602210008499044</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-02-21 00:08:49</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:11007</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>L202602210008581326</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-02-21 00:08:58</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/operation_logs.xlsx
+++ b/operation_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -750,6 +750,72 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L202602210023099567</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-02-21 00:23:09</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 4</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L202602210035444441</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-02-21 00:35:44</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>从 SFTP 服务器恢复数据</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/operation_logs.xlsx
+++ b/operation_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,12 +456,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L202602210000537663</t>
+          <t>L202602252251586497</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-21 00:00:53</t>
+          <t>2026-02-25 22:51:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,7 +476,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:22</t>
+          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:11007</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -489,12 +489,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L202602210002006269</t>
+          <t>L202602252252282981</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-21 00:02:00</t>
+          <t>2026-02-25 22:52:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:11007</t>
+          <t>上传数据到 SFTP 服务器，版本: 3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -522,12 +522,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L202602210002163137</t>
+          <t>L202602262201016423</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-21 00:02:16</t>
+          <t>2026-02-26 22:01:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:11007</t>
+          <t>上传数据到 SFTP 服务器，版本: 4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -555,12 +555,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L202602210003001118</t>
+          <t>L202602270012269693</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-02-21 00:03:00</t>
+          <t>2026-02-27 00:12:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上传数据到 SFTP 服务器，版本: 1</t>
+          <t>上传数据到 SFTP 服务器，版本: 5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -588,12 +588,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L202602210004592866</t>
+          <t>L202603032243235563</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-02-21 00:04:59</t>
+          <t>2026-03-03 22:43:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:1100</t>
+          <t>上传数据到 SFTP 服务器，版本: 6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -621,12 +621,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L202602210006508651</t>
+          <t>L202603092010321014</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:06:50</t>
+          <t>2026-03-09 20:10:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:11007</t>
+          <t>上传数据到 SFTP 服务器，版本: 7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -654,12 +654,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L202602210007157100</t>
+          <t>L202603202213223487</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-02-21 00:07:15</t>
+          <t>2026-03-20 22:13:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -674,143 +674,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>上传数据到 SFTP 服务器，版本: 2</t>
+          <t>从 SFTP 服务器恢复数据</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>系统</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>L202602210008499044</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-02-21 00:08:49</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>云端同步</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>配置 SFTP 服务器: 27.tcp.cpolar.top:11007</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>系统</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>L202602210008581326</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-02-21 00:08:58</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>云端同步</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>上传数据到 SFTP 服务器，版本: 3</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>系统</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>L202602210023099567</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-02-21 00:23:09</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>云端同步</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>上传数据到 SFTP 服务器，版本: 4</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>系统</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>L202602210035444441</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-02-21 00:35:44</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>云端同步</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>从 SFTP 服务器恢复数据</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
         <is>
           <t>系统</t>
         </is>

--- a/operation_logs.xlsx
+++ b/operation_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,6 +684,72 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L202604251703318075</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-25 17:03:31</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>配置 SFTP 服务器: 6.tcp.cpolar.top:13950</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>L202604251704493778</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-25 17:04:49</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/operation_logs.xlsx
+++ b/operation_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -750,6 +750,72 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L202605060045415287</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:45:41</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>从 SFTP 服务器恢复数据</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L202605060051109550</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:51:10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/operation_logs.xlsx
+++ b/operation_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -816,6 +816,39 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L202605091236478131</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:36:47</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 4</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/operation_logs.xlsx
+++ b/operation_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -849,6 +849,39 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>L202605101836574502</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-10 18:36:57</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 5</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/operation_logs.xlsx
+++ b/operation_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,6 +882,72 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>L202605101904508176</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-10 19:04:50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 6</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>L202605120212209125</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:12:20</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 7</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/operation_logs.xlsx
+++ b/operation_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +948,39 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>L202605191637346316</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-19 16:37:34</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 8</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/operation_logs.xlsx
+++ b/operation_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -951,12 +951,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L202605191637346316</t>
+          <t>L202605200018598257</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-05-19 16:37:34</t>
+          <t>2026-05-20 00:18:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -971,11 +971,143 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>上传数据到 SFTP 服务器，版本: 8</t>
+          <t>从 SFTP 服务器恢复数据</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>L202605200021091805</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-20 00:21:09</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 9</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>L202605271658159051</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:58:15</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 10</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>L202605271701278254</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-27 17:01:27</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 11</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>L202606181657417724</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-18 16:57:41</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 12</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>系统</t>
         </is>

--- a/operation_logs.xlsx
+++ b/operation_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1083,12 +1083,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L202606181657417724</t>
+          <t>L202606261915391267</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-18 16:57:41</t>
+          <t>2026-06-26 19:15:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1103,11 +1103,44 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>上传数据到 SFTP 服务器，版本: 12</t>
+          <t>从 SFTP 服务器恢复数据</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>L202606261917439348</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-26 19:17:43</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>云端同步</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>上传数据到 SFTP 服务器，版本: 13</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
